--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="447" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B606872-97C9-4731-B4C5-BF16F7F083FE}"/>
+  <xr:revisionPtr revIDLastSave="463" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4849B5-5940-4860-94F5-561D25705936}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="122">
   <si>
     <t>Date</t>
   </si>
@@ -451,6 +451,24 @@
   </si>
   <si>
     <t>Useful, demonstrates use of magic numbers for file signatures.</t>
+  </si>
+  <si>
+    <t>What parameters can be set for Ais, what are best practices?</t>
+  </si>
+  <si>
+    <t>6 sources found and briefly examined</t>
+  </si>
+  <si>
+    <t>https://www.ibm.com/think/topics/model-parameters</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s44163-025-00729-4</t>
+  </si>
+  <si>
+    <t>Not forensics specific, but still solid for genearal Machine Learning.</t>
+  </si>
+  <si>
+    <t>Not particularly useful, seems intended for building an LLM rather than tweaking an existing one's parameters.</t>
   </si>
 </sst>
 </file>
@@ -838,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G68"/>
+  <dimension ref="B2:G72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -857,7 +875,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1853,6 +1871,57 @@
         <v>114</v>
       </c>
     </row>
+    <row r="70" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B70" s="2">
+        <v>46281</v>
+      </c>
+      <c r="C70" s="1">
+        <v>10</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B71" s="2">
+        <v>46281</v>
+      </c>
+      <c r="C71" s="1">
+        <v>20</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="C72" s="1">
+        <v>30</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="463" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4849B5-5940-4860-94F5-561D25705936}"/>
+  <xr:revisionPtr revIDLastSave="535" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE37DFC-4B83-43C1-9D2F-61537413123C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25155" yWindow="4500" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="142">
   <si>
     <t>Date</t>
   </si>
@@ -468,7 +468,67 @@
     <t>Not forensics specific, but still solid for genearal Machine Learning.</t>
   </si>
   <si>
-    <t>Not particularly useful, seems intended for building an LLM rather than tweaking an existing one's parameters.</t>
+    <t>How does the QUIC transport protocol work?</t>
+  </si>
+  <si>
+    <t>Useful for if QUIC protocols show up in the Nmap or Wireshark scans.</t>
+  </si>
+  <si>
+    <t>https://www.rfc-editor.org/info/rfc9000/</t>
+  </si>
+  <si>
+    <t>How does subnetting work (to find address for nmap)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZxAwQB8TZsM</t>
+  </si>
+  <si>
+    <t>Somewhat useful, although seems more intended for building an LLM rather than tweaking an existing one's parameters.</t>
+  </si>
+  <si>
+    <t>Somewhat useful, although it does the process in reverse (I needed to get the /24 number on the end, not start from it.</t>
+  </si>
+  <si>
+    <t>How to make an Nmap report.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=7621YgRdqHw</t>
+  </si>
+  <si>
+    <t>Useful, was running scans myself in the background, pausing the video for my scans to catch up. Solid source for Nmap's workings</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=RvC564r5hl4</t>
+  </si>
+  <si>
+    <t>Useful, showed how to export the scan information as an XML file.</t>
+  </si>
+  <si>
+    <t>Why does the LLM output txt file have ANSI characters at the end of each line?</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/ANSI_escape_code</t>
+  </si>
+  <si>
+    <t>https://genai.owasp.org/llmrisk/llm052025-improper-output-handling/</t>
+  </si>
+  <si>
+    <t>Not particularly useful for resovling the issue, but still good information to know.</t>
+  </si>
+  <si>
+    <t>https://embracethered.com/blog/posts/2024/terminal-dillmas-prompt-injection-ansi-sequences/</t>
+  </si>
+  <si>
+    <t>Similar to the above source, good info but a different issue.</t>
+  </si>
+  <si>
+    <t>Useful, explains what the various symbols mean.</t>
+  </si>
+  <si>
+    <t>https://code.mendhak.com/how-do-terminal-progress-bars-actually-work/</t>
+  </si>
+  <si>
+    <t>Useful, explains why the symbols are showing up.</t>
   </si>
 </sst>
 </file>
@@ -856,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G72"/>
+  <dimension ref="B2:G84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -875,7 +935,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -887,7 +947,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1909,6 +1969,9 @@
       </c>
     </row>
     <row r="72" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B72" s="2">
+        <v>46281</v>
+      </c>
       <c r="C72" s="1">
         <v>30</v>
       </c>
@@ -1916,10 +1979,190 @@
         <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C74" s="1">
+        <v>30</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B75" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C75" s="1">
+        <v>20</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B77" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C77" s="1">
+        <v>20</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="2">
+        <v>46284</v>
+      </c>
+      <c r="C78" s="1">
+        <v>10</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B80" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C80" s="1">
+        <v>10</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B81" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C81" s="1">
+        <v>10</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C82" s="1">
+        <v>5</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C83" s="1">
+        <v>15</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C84" s="1">
+        <v>10</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="535" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE37DFC-4B83-43C1-9D2F-61537413123C}"/>
+  <xr:revisionPtr revIDLastSave="537" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23694193-A159-53FA-9679-D9366D1DC273}"/>
   <bookViews>
-    <workbookView xWindow="-25155" yWindow="4500" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -647,10 +647,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="537" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23694193-A159-53FA-9679-D9366D1DC273}"/>
+  <xr:revisionPtr revIDLastSave="561" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A7D540-F4F9-43AB-83F8-E7606DF1946B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -513,9 +513,6 @@
     <t>https://genai.owasp.org/llmrisk/llm052025-improper-output-handling/</t>
   </si>
   <si>
-    <t>Not particularly useful for resovling the issue, but still good information to know.</t>
-  </si>
-  <si>
     <t>https://embracethered.com/blog/posts/2024/terminal-dillmas-prompt-injection-ansi-sequences/</t>
   </si>
   <si>
@@ -529,6 +526,33 @@
   </si>
   <si>
     <t>Useful, explains why the symbols are showing up.</t>
+  </si>
+  <si>
+    <t>How to use Adobe Illustrator (for making the poster)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3NBKRywEbNs</t>
+  </si>
+  <si>
+    <t>Watching, Experimenting</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=uKdo9OkLzzo</t>
+  </si>
+  <si>
+    <t>Useful, covered the basics. Experimenting with the various tools helped quite a bit.</t>
+  </si>
+  <si>
+    <t>Not particularly useful for resolving the issue, but still good information to know.</t>
+  </si>
+  <si>
+    <t>Useful, showed how the Properties menu can be used to edit shapes easier</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iQWTSupSrko</t>
+  </si>
+  <si>
+    <t>Very useful. Showed exactly what each tool is used for and how to do it.</t>
   </si>
 </sst>
 </file>
@@ -647,6 +671,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -912,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G84"/>
+  <dimension ref="B2:G88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -931,7 +959,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -2095,7 +2123,7 @@
         <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>135</v>
@@ -2115,10 +2143,10 @@
         <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.25">
@@ -2135,7 +2163,7 @@
         <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>134</v>
@@ -2155,10 +2183,70 @@
         <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B86" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C86" s="1">
+        <v>45</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>140</v>
+      <c r="F86" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C87" s="1">
+        <v>15</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B88" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C88" s="1">
+        <v>60</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="561" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A7D540-F4F9-43AB-83F8-E7606DF1946B}"/>
+  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CAF56D5-3A77-4CF7-BBC7-25088DAEFCBD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1920" yWindow="1005" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="166">
   <si>
     <t>Date</t>
   </si>
@@ -553,6 +553,54 @@
   </si>
   <si>
     <t>Very useful. Showed exactly what each tool is used for and how to do it.</t>
+  </si>
+  <si>
+    <t>How to make an academic poster</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8Rzn9juaZ9c</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2049080116301303</t>
+  </si>
+  <si>
+    <t>https://libguides.tru.ca/academicposters/home</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=r6jJPT_dr3k</t>
+  </si>
+  <si>
+    <t>Useful, told me how much information to put down, what is too much.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ZwiTqrVfDFU</t>
+  </si>
+  <si>
+    <t>Somewhat useful, had good tips on layout and spacing.</t>
+  </si>
+  <si>
+    <t>Useful, explains how to lay things out for readability. Minimal words is key. Lots of figures is essential to retain viewer attention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Useful, says to keep wording simple and to minimize jargon. Keep it simple. </t>
+  </si>
+  <si>
+    <t>Useful, gives insight into colour schemes and approximate sizes of each section.</t>
+  </si>
+  <si>
+    <t>How to make a report on a PCAP file.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=e06bi_pOIuY</t>
+  </si>
+  <si>
+    <t>Very useful, showed how to make the report and useful sections to have.</t>
+  </si>
+  <si>
+    <t>Kent, K., Chevalier, S., Grance, T., &amp; Dang, H. (2006). Guide to integrating forensic techniques into incident response (NIST Special Publication 800-86). National Institute of Standards and Technology. https://doi.org/10.6028/NIST.SP.800-86</t>
+  </si>
+  <si>
+    <t>Useful, explained the process of examination, analysis, and reporting.</t>
   </si>
 </sst>
 </file>
@@ -940,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G88"/>
+  <dimension ref="B2:G97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -958,8 +1006,8 @@
         <v>3</v>
       </c>
       <c r="D2" s="4">
-        <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>23</v>
+        <f>ROUNDDOWN(SUM(C7:C502)/60,0)</f>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -970,8 +1018,8 @@
         <v>4</v>
       </c>
       <c r="D3" s="4">
-        <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>50</v>
+        <f>ROUND(MOD(SUM(C7:C502),60),0)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2249,6 +2297,146 @@
         <v>148</v>
       </c>
     </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B90" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C90" s="1">
+        <v>20</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B91" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C91" s="1">
+        <v>25</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B92" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C92" s="1">
+        <v>15</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B93" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C93" s="1">
+        <v>10</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B94" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C94" s="1">
+        <v>10</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B96" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C96" s="1">
+        <v>60</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B97" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C97" s="1">
+        <v>45</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="613" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CAF56D5-3A77-4CF7-BBC7-25088DAEFCBD}"/>
+  <xr:revisionPtr revIDLastSave="622" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F45F2C0-F9E8-4826-AEAD-22C0474A5F15}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1920" yWindow="1005" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="169">
   <si>
     <t>Date</t>
   </si>
@@ -601,6 +601,15 @@
   </si>
   <si>
     <t>Useful, explained the process of examination, analysis, and reporting.</t>
+  </si>
+  <si>
+    <t>How Nmap is used practically in pen testing</t>
+  </si>
+  <si>
+    <t>Somewhat useful. Showed good commands and expected outputs.</t>
+  </si>
+  <si>
+    <t>After the meeting, Bryce wanted to talk to Olivia and Matt about the Pen Testing course, advised I stick around for Nmap research.</t>
   </si>
 </sst>
 </file>
@@ -988,7 +997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G97"/>
+  <dimension ref="B2:G99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1007,7 +1016,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C502)/60,0)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1019,7 +1028,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C502),60),0)</f>
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2437,6 +2446,26 @@
         <v>164</v>
       </c>
     </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C99" s="1">
+        <v>30</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="622" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F45F2C0-F9E8-4826-AEAD-22C0474A5F15}"/>
+  <xr:revisionPtr revIDLastSave="729" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC23E6F6-B4F5-42AF-A8B2-9454B5009170}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="198">
   <si>
     <t>Date</t>
   </si>
@@ -609,7 +609,117 @@
     <t>Somewhat useful. Showed good commands and expected outputs.</t>
   </si>
   <si>
-    <t>After the meeting, Bryce wanted to talk to Olivia and Matt about the Pen Testing course, advised I stick around for Nmap research.</t>
+    <t>Other ways AI vs Human reporting has been done</t>
+  </si>
+  <si>
+    <t>After the meeting, Bryce wanted to talk to Olivia and Matt about the Pen Testing course, and suggested I stick around for the Nmap bits of the talk.</t>
+  </si>
+  <si>
+    <t>https://libguides.derby.ac.uk/develop-at-derby/resilience/reflective-models</t>
+  </si>
+  <si>
+    <t>Useful, showed the Experience/Reflection/Action method, What/SoWhat/NowWhat, and Gibbs Reflective models.</t>
+  </si>
+  <si>
+    <t>Similar to the above, but also included Kolb's experiential learning cycle.</t>
+  </si>
+  <si>
+    <t>https://libguides.cam.ac.uk/reflectivepracticetoolkit/models</t>
+  </si>
+  <si>
+    <t>What models of writing reflections are there?</t>
+  </si>
+  <si>
+    <t>https://reflectivewriting.tips/models-of-reflection-you-can-use/</t>
+  </si>
+  <si>
+    <t>Contained much of the same information as the above resource.</t>
+  </si>
+  <si>
+    <t>Lockwood, A. B., Farmer, R. L., Shergill, G., Benson, N. F., &amp; Gilbert, K. (2024). Human vs. machine: Comparing AI-generated and human-written psychological reports [Preprint]. OSF. https://osf.io/83jv2/</t>
+  </si>
+  <si>
+    <t>Not forensics content, and not peer reviewed, but is solid for evaluating AI vs Human produced content.</t>
+  </si>
+  <si>
+    <t>Useful metrics to be measuring for the tests</t>
+  </si>
+  <si>
+    <t>https://www.auckland.ac.nz/en/research/research-resources/publishing-communication-profiles/metrics-academic-impact/introduction-metrics.html</t>
+  </si>
+  <si>
+    <t>Not useful, seems to be more about tracking an author's reputation/reliability?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Useful metrics to be measuring for the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tests</t>
+    </r>
+  </si>
+  <si>
+    <t>https://www.growthbook.io/insights/how-measure-quality-ai-outputs-beyond-accuracy</t>
+  </si>
+  <si>
+    <t>Useful! Potential other metrics to use: Usefulness, relevance, hallucination rate, task completion, safety, latency, user satisfaction. Aimed at LLM chats rather than created reports, but still applicable.</t>
+  </si>
+  <si>
+    <t>Relevance, Accuracy Clarity, Bias, Comprehensiveness, Confidence when lacking info.</t>
+  </si>
+  <si>
+    <t>https://clarivate.com/academia-government/blog/evaluating-the-quality-of-generative-ai-output-methods-metrics-and-best-practices/</t>
+  </si>
+  <si>
+    <t>https://mlflow.org/articles/types-of-ai-model-evaluation-metrics/</t>
+  </si>
+  <si>
+    <t>Again, intended for models themselves rather than output, but still useful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor content, and based on LLM apps rather than output. Has good rules such as having no more than 5 metrics though. </t>
+  </si>
+  <si>
+    <t>https://www.confident-ai.com/blog/llm-evaluation-metrics-everything-you-need-for-llm-evaluation</t>
+  </si>
+  <si>
+    <t>How to make a Gantt chat look better?</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=iDZdOepwtmk</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JH5MeU2QPs4</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=W038AccGgg8</t>
+  </si>
+  <si>
+    <t>Not as useful as the other videos, was more about basic usage.</t>
+  </si>
+  <si>
+    <t>Useful, showed colour coding for different tasks</t>
+  </si>
+  <si>
+    <t>Useful, showed how to make groupings/headers with the tasks.</t>
   </si>
 </sst>
 </file>
@@ -686,7 +796,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -712,6 +822,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -997,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G99"/>
+  <dimension ref="B2:G113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1015,8 +1126,8 @@
         <v>3</v>
       </c>
       <c r="D2" s="4">
-        <f>ROUNDDOWN(SUM(C7:C502)/60,0)</f>
-        <v>27</v>
+        <f>ROUNDDOWN(SUM(C7:C503)/60,0)</f>
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1027,7 +1138,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="4">
-        <f>ROUND(MOD(SUM(C7:C502),60),0)</f>
+        <f>ROUND(MOD(SUM(C7:C503),60),0)</f>
         <v>25</v>
       </c>
     </row>
@@ -2446,7 +2557,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B99" s="2">
         <v>46297</v>
       </c>
@@ -2463,10 +2574,242 @@
         <v>167</v>
       </c>
       <c r="G99" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B100" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C100" s="1">
+        <v>10</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C101" s="1">
+        <v>10</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B104" s="2">
+        <v>46298</v>
+      </c>
+      <c r="C104" s="1">
+        <v>45</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>168</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B106" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C106" s="1">
+        <v>5</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B107" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C107" s="1">
+        <v>20</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B108" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C108" s="1">
+        <v>15</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B109" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C109" s="1">
+        <v>10</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B110" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C110" s="1">
+        <v>30</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B111" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C111" s="1">
+        <v>10</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B112" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C112" s="1">
+        <v>10</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B113" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C113" s="1">
+        <v>10</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="729" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC23E6F6-B4F5-42AF-A8B2-9454B5009170}"/>
+  <xr:revisionPtr revIDLastSave="730" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F7594E1-A8E2-4330-96E9-197B0530684A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1005" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="179">
   <si>
     <t>Date</t>
   </si>
@@ -640,86 +640,6 @@
   </si>
   <si>
     <t>Not forensics content, and not peer reviewed, but is solid for evaluating AI vs Human produced content.</t>
-  </si>
-  <si>
-    <t>Useful metrics to be measuring for the tests</t>
-  </si>
-  <si>
-    <t>https://www.auckland.ac.nz/en/research/research-resources/publishing-communication-profiles/metrics-academic-impact/introduction-metrics.html</t>
-  </si>
-  <si>
-    <t>Not useful, seems to be more about tracking an author's reputation/reliability?</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Useful metrics to be measuring for the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>LLM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tests</t>
-    </r>
-  </si>
-  <si>
-    <t>https://www.growthbook.io/insights/how-measure-quality-ai-outputs-beyond-accuracy</t>
-  </si>
-  <si>
-    <t>Useful! Potential other metrics to use: Usefulness, relevance, hallucination rate, task completion, safety, latency, user satisfaction. Aimed at LLM chats rather than created reports, but still applicable.</t>
-  </si>
-  <si>
-    <t>Relevance, Accuracy Clarity, Bias, Comprehensiveness, Confidence when lacking info.</t>
-  </si>
-  <si>
-    <t>https://clarivate.com/academia-government/blog/evaluating-the-quality-of-generative-ai-output-methods-metrics-and-best-practices/</t>
-  </si>
-  <si>
-    <t>https://mlflow.org/articles/types-of-ai-model-evaluation-metrics/</t>
-  </si>
-  <si>
-    <t>Again, intended for models themselves rather than output, but still useful.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor content, and based on LLM apps rather than output. Has good rules such as having no more than 5 metrics though. </t>
-  </si>
-  <si>
-    <t>https://www.confident-ai.com/blog/llm-evaluation-metrics-everything-you-need-for-llm-evaluation</t>
-  </si>
-  <si>
-    <t>How to make a Gantt chat look better?</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=iDZdOepwtmk</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=JH5MeU2QPs4</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=W038AccGgg8</t>
-  </si>
-  <si>
-    <t>Not as useful as the other videos, was more about basic usage.</t>
-  </si>
-  <si>
-    <t>Useful, showed colour coding for different tasks</t>
-  </si>
-  <si>
-    <t>Useful, showed how to make groupings/headers with the tasks.</t>
   </si>
 </sst>
 </file>
@@ -796,7 +716,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -822,7 +742,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1108,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G113"/>
+  <dimension ref="B2:G104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1127,7 +1046,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C503)/60,0)</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1139,7 +1058,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C503),60),0)</f>
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2613,7 +2532,7 @@
       <c r="F101" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G101" s="9" t="s">
+      <c r="G101" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2633,7 +2552,7 @@
       <c r="F102" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G102" s="9" t="s">
+      <c r="G102" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2653,159 +2572,8 @@
       <c r="F104" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G104" s="9" t="s">
+      <c r="G104" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B106" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C106" s="1">
-        <v>5</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B107" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C107" s="1">
-        <v>20</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B108" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C108" s="1">
-        <v>15</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B109" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C109" s="1">
-        <v>10</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B110" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C110" s="1">
-        <v>30</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B111" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C111" s="1">
-        <v>10</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B112" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C112" s="1">
-        <v>10</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B113" s="2">
-        <v>46300</v>
-      </c>
-      <c r="C113" s="1">
-        <v>10</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
